--- a/skills/api-orchestrator/platforms/easyops/hub/monitor-kits/路由器监控_告警规则模板.xlsx
+++ b/skills/api-orchestrator/platforms/easyops/hub/monitor-kits/路由器监控_告警规则模板.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_cpu_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 80, "displayThreshold": 80, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_memory_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "warning", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 75, "displayThreshold": 75, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_temperature_val", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "critical", "threshold": 1, "displayThreshold": 1, "tolerance": 0, "type": "unequal"}], "detectWindow": 3, "metricName": "snmp_netware_fan_status", "mode": "static", "recoverCount": 0, "type": "unequal"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "critical", "threshold": 1, "displayThreshold": 1, "tolerance": 0, "type": "unequal"}], "detectWindow": 3, "metricName": "snmp_netware_power_status", "mode": "static", "recoverCount": 0, "type": "unequal"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "critical", "threshold": 1, "displayThreshold": 1, "tolerance": 0, "type": "unequal"}], "detectWindow": 3, "metricName": "m_port_oper_status", "mode": "static", "recoverCount": 0, "type": "unequal"}]</t>
+          <t>[{"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_cpu_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 80, "displayThreshold": 80, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_memory_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "warning", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 75, "displayThreshold": 75, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_temperature_val", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_fan_status", "mode": "static", "recoverCount": 3, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_power_status", "mode": "static", "recoverCount": 3, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "m_port_oper_status", "mode": "static", "recoverCount": 3, "type": "diff"}]</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">

--- a/skills/api-orchestrator/platforms/easyops/hub/monitor-kits/路由器监控_告警规则模板.xlsx
+++ b/skills/api-orchestrator/platforms/easyops/hub/monitor-kits/路由器监控_告警规则模板.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_cpu_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 80, "displayThreshold": 80, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_memory_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "warning", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 75, "displayThreshold": 75, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_temperature_val", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_fan_status", "mode": "static", "recoverCount": 3, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_power_status", "mode": "static", "recoverCount": 3, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "m_port_oper_status", "mode": "static", "recoverCount": 3, "type": "diff"}]</t>
+          <t>[{"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_cpu_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 80, "displayThreshold": 80, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_memory_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "warning", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 75, "displayThreshold": 75, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_temperature_val", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_fan_status", "mode": "static", "recoverCount": 0, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_power_status", "mode": "static", "recoverCount": 0, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "m_port_oper_status", "mode": "static", "recoverCount": 0, "type": "diff"}]</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">

--- a/skills/api-orchestrator/platforms/easyops/hub/monitor-kits/路由器监控_告警规则模板.xlsx
+++ b/skills/api-orchestrator/platforms/easyops/hub/monitor-kits/路由器监控_告警规则模板.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_cpu_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 80, "displayThreshold": 80, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_memory_utilization", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "warning", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 75, "displayThreshold": 75, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_temperature_val", "mode": "static", "recoverCount": 0, "type": "bigger_than"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_fan_status", "mode": "static", "recoverCount": 0, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_power_status", "mode": "static", "recoverCount": 0, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "m_port_oper_status", "mode": "static", "recoverCount": 0, "type": "diff"}]</t>
+          <t>[{"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_cpu_utilization", "mode": "static", "recoverCount": 1, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "info", "threshold": 70, "displayThreshold": 70, "tolerance": 0, "type": "bigger_than"}, {"level": "warning", "threshold": 80, "displayThreshold": 80, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 90, "displayThreshold": 90, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_memory_utilization", "mode": "static", "recoverCount": 1, "type": "bigger_than"}, {"alertCount": 3, "alertDims": null, "comparators": [{"level": "warning", "threshold": 60, "displayThreshold": 60, "tolerance": 0, "type": "bigger_than"}, {"level": "critical", "threshold": 75, "displayThreshold": 75, "tolerance": 0, "type": "bigger_than"}], "detectWindow": 3, "metricName": "snmp_netware_temperature_val", "mode": "static", "recoverCount": 1, "type": "bigger_than"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_fan_status", "mode": "static", "recoverCount": 0, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "snmp_netware_power_status", "mode": "static", "recoverCount": 0, "type": "diff"}, {"alertCount": 1, "alertDims": [], "comparators": [{"displayThreshold": [null, null], "displayUnit": "", "level": "warning", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}, {"displayThreshold": [null, null], "displayUnit": "", "level": "critical", "params": [{"key": "offset", "value": 0}, {"key": "window", "value": 8}], "threshold": [null, null], "tolerance": 0}], "detectWindow": 1, "metricName": "m_port_oper_status", "mode": "static", "recoverCount": 0, "type": "diff"}]</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
